--- a/evaluation/gpt_domain.xlsx
+++ b/evaluation/gpt_domain.xlsx
@@ -333,7 +333,7 @@
     <col width="36.300000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="26.400000000000002" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.06986370919713651</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.028703089142484234</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.415007806401249</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>0.36918175090963323</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.7642857142857142</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>0.7722395614865794</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="6">
@@ -449,7 +449,7 @@
         <v>0.0744863314110034</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.0029411764705882353</v>
+        <v>0.2904614139233675</v>
       </c>
     </row>
     <row r="8">
@@ -465,7 +465,7 @@
         <v>0.4634660664110746</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.35</v>
+        <v>0.64375</v>
       </c>
     </row>
     <row r="9">
@@ -481,7 +481,7 @@
         <v>0.4297738391517053</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.4142857142857143</v>
+        <v>0.7071428571428572</v>
       </c>
     </row>
     <row r="10">
@@ -513,7 +513,7 @@
         <v>0.771408411398117</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.14444444444444446</v>
+        <v>0.49905149051490516</v>
       </c>
     </row>
     <row r="12">
@@ -529,7 +529,7 @@
         <v>0.3671073782476683</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.19727891156462585</v>
+        <v>0.49863945578231295</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         <v>0.92955711169917</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         <v>0.8491502727720733</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
     </row>
     <row r="15">
@@ -593,7 +593,7 @@
         <v>0.32589175953011573</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.1283068783068783</v>
+        <v>0.5029289493575207</v>
       </c>
     </row>
     <row r="17">
@@ -609,7 +609,7 @@
         <v>0.08450426027607655</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
     </row>
     <row r="18">
@@ -625,7 +625,7 @@
         <v>0.45036453356892464</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.18207718207718207</v>
+        <v>0.5126072184895715</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>0.9018724962079787</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.30518518518518517</v>
+        <v>0.5162289562289563</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         <v>0.0</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.0</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +673,7 @@
         <v>0.5750675939670482</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.3327380952380953</v>
+        <v>0.5189331501831502</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +689,7 @@
         <v>0.7984476718786792</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.1326388888888889</v>
+        <v>0.4774305555555555</v>
       </c>
     </row>
     <row r="23">
@@ -705,7 +705,7 @@
         <v>0.446228015923701</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.0068936877076411955</v>
+        <v>0.29756449091264414</v>
       </c>
     </row>
     <row r="24">
@@ -737,7 +737,7 @@
         <v>0.10794704599197937</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.0880952380952381</v>
+        <v>0.42946428571428574</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/gpt_domain.xlsx
+++ b/evaluation/gpt_domain.xlsx
@@ -333,7 +333,7 @@
     <col width="36.300000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="26.400000000000002" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.06986370919713651</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.028703089142484234</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.415007806401249</v>
+        <v>0.04586260733801717</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>0.36918175090963323</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.7642857142857142</v>
+        <v>0.5285714285714286</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>0.7722395614865794</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -449,7 +449,7 @@
         <v>0.0744863314110034</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.2904614139233675</v>
+        <v>0.0016999460334592553</v>
       </c>
     </row>
     <row r="8">
@@ -465,7 +465,7 @@
         <v>0.4634660664110746</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.64375</v>
+        <v>0.328125</v>
       </c>
     </row>
     <row r="9">
@@ -481,7 +481,7 @@
         <v>0.4297738391517053</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.7071428571428572</v>
+        <v>0.4142857142857143</v>
       </c>
     </row>
     <row r="10">
@@ -513,7 +513,7 @@
         <v>0.771408411398117</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.49905149051490516</v>
+        <v>0.12330623306233063</v>
       </c>
     </row>
     <row r="12">
@@ -529,7 +529,7 @@
         <v>0.3671073782476683</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.49863945578231295</v>
+        <v>0.1578231292517007</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         <v>0.92955711169917</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         <v>0.8491502727720733</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
     </row>
     <row r="15">
@@ -593,7 +593,7 @@
         <v>0.32589175953011573</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.5029289493575207</v>
+        <v>0.1125958319835871</v>
       </c>
     </row>
     <row r="17">
@@ -609,7 +609,7 @@
         <v>0.08450426027607655</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
     </row>
     <row r="18">
@@ -625,7 +625,7 @@
         <v>0.45036453356892464</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.5126072184895715</v>
+        <v>0.15351605547683977</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>0.9018724962079787</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.5162289562289563</v>
+        <v>0.22195286195286196</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         <v>0.0</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.375</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +673,7 @@
         <v>0.5750675939670482</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.5189331501831502</v>
+        <v>0.23462301587301587</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +689,7 @@
         <v>0.7984476718786792</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.4774305555555555</v>
+        <v>0.10905864197530864</v>
       </c>
     </row>
     <row r="23">
@@ -705,7 +705,7 @@
         <v>0.446228015923701</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.29756449091264414</v>
+        <v>0.004055110416259527</v>
       </c>
     </row>
     <row r="24">
@@ -737,7 +737,7 @@
         <v>0.10794704599197937</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.42946428571428574</v>
+        <v>0.06790674603174604</v>
       </c>
     </row>
   </sheetData>
